--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6464-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6464-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB278B00-55CF-4914-8B4E-37D7D5C30E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDC430F4-7EB5-4CD0-8129-AFD5C6E7CC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{91F40E24-231A-4DE0-815A-C8777A25EE26}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{ACE03013-E307-44F4-A008-235C27C2A31F}"/>
   </bookViews>
   <sheets>
     <sheet name="6464-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1547,28 +1547,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F581E352-6076-45A3-B0DD-4C792D684D95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B36FBC8-1ACA-4541-84C5-42D44ABD15CA}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.125" customWidth="1"/>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="7" width="6.75" customWidth="1"/>
-    <col min="8" max="8" width="6.375" customWidth="1"/>
-    <col min="9" max="10" width="6.75" customWidth="1"/>
-    <col min="11" max="13" width="6.375" customWidth="1"/>
-    <col min="14" max="15" width="6.75" customWidth="1"/>
-    <col min="16" max="18" width="6.375" customWidth="1"/>
-    <col min="19" max="19" width="6.75" customWidth="1"/>
-    <col min="20" max="20" width="6.375" customWidth="1"/>
-    <col min="21" max="21" width="7.625" customWidth="1"/>
-    <col min="22" max="22" width="6.375" customWidth="1"/>
-    <col min="23" max="23" width="7.625" customWidth="1"/>
-    <col min="24" max="24" width="7.75" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="W1" s="33"/>
       <c r="X1" s="25"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1758,7 +1758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>2025</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="42">
         <v>2024</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="44"/>
       <c r="B8" s="45"/>
       <c r="C8" s="18" t="s">
@@ -2004,7 +2004,7 @@
       <c r="W8" s="51"/>
       <c r="X8" s="47"/>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="48" t="s">
         <v>29</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="49"/>
       <c r="B10" s="49"/>
       <c r="C10" s="20" t="s">
@@ -2106,7 +2106,7 @@
       <c r="W10" s="51"/>
       <c r="X10" s="47"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2023</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="54">
         <v>2022</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2021</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="54">
         <v>2020</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2019</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="54">
         <v>2018</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2017</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="54">
         <v>2016</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>2015</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="54">
         <v>2014</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>2013</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="54" t="s">
         <v>53</v>
       </c>
